--- a/tams-svreport-batch/tams-svreport-batch-chb3/src/main/resources/tpl/EquityBusiInfoRegistCHB.xlsx
+++ b/tams-svreport-batch/tams-svreport-batch-chb3/src/main/resources/tpl/EquityBusiInfoRegistCHB.xlsx
@@ -5,30 +5,30 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\feature3.0.6\tams\tams-svreport-batch\tams-svreport-batch-chb3\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\svn管理\3.0.6需求\增量需求\中债7月将升级\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="12795"/>
+    <workbookView xWindow="948" yWindow="0" windowWidth="17220" windowHeight="7776"/>
   </bookViews>
   <sheets>
-    <sheet name="投资者明细信息登记" sheetId="1" r:id="rId1"/>
+    <sheet name="业务明细信息登记" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
     <sheet name="版本号1.0.0" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="bz">填写说明!$A$143:$A$320</definedName>
     <definedName name="gmd">填写说明!$A$7:$A$46</definedName>
-    <definedName name="qd">填写说明!$A$323:$A$329</definedName>
+    <definedName name="qd">填写说明!$A$323:$A$331</definedName>
     <definedName name="ywzl">填写说明!$A$89:$A$104</definedName>
     <definedName name="关联账户所在地">填写说明!$A$7:$A$46</definedName>
   </definedNames>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="328">
   <si>
     <t>**发行机构代码</t>
   </si>
@@ -137,6 +137,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.为使导入成功，所有单元格都必须保持模板原有的格式，如须粘贴数据请使用</t>
@@ -146,6 +147,7 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“选择性粘贴”</t>
@@ -155,6 +157,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>并只</t>
@@ -164,6 +167,7 @@
         <sz val="12"/>
         <color indexed="10"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>“粘贴数值”</t>
@@ -1027,6 +1031,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>1.</t>
@@ -1036,6 +1041,7 @@
         <sz val="11"/>
         <color indexed="8"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>0.0</t>
@@ -1049,6 +1055,26 @@
   </si>
   <si>
     <t>1.新增业务明细信息登记模板</t>
+  </si>
+  <si>
+    <t>**交易序列号</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>**关联活期存款账号开户行代码</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>**关联活期存款账号开户行名称</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>07 银联交易</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>08 第三方支付</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1065,12 +1091,14 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1078,23 +1106,27 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1102,23 +1134,27 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1258,7 +1294,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1352,10 +1388,9 @@
     <xf numFmtId="49" fontId="7" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1704,27 +1739,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:AD1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="22.625" style="28" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="22.69921875" style="28" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="18" style="28" customWidth="1" collapsed="1"/>
-    <col min="3" max="14" width="26.125" style="28" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="19.375" style="28" customWidth="1" collapsed="1"/>
-    <col min="17" max="18" width="26.125" style="28" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="18.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="20" max="20" width="26.125" style="28" customWidth="1" collapsed="1"/>
-    <col min="21" max="21" width="18.375" style="28" customWidth="1" collapsed="1"/>
-    <col min="22" max="22" width="19.375" style="28" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="17.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="24" style="28" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="15.5" style="28" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="16.875" style="28" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="17.375" style="28" customWidth="1" collapsed="1"/>
-    <col min="28" max="16384" width="9" style="29" collapsed="1"/>
+    <col min="3" max="9" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
+    <col min="10" max="11" width="32.09765625" style="28" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="12" max="17" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
+    <col min="18" max="19" width="19.3984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="20" max="21" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
+    <col min="22" max="22" width="18.5" style="28" customWidth="1" collapsed="1"/>
+    <col min="23" max="23" width="26.09765625" style="28" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="18.3984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="19.3984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="17.5" style="28" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="24" style="28" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="15.5" style="28" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="16.8984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="30" max="30" width="17.3984375" style="28" customWidth="1" collapsed="1"/>
+    <col min="31" max="16384" width="9" style="29" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:30">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -1747,106 +1784,86 @@
         <v>6</v>
       </c>
       <c r="H1" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="I1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="J1" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="L1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="M1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="N1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="O1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="P1" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="Q1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="R1" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="S1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="T1" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="U1" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="V1" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="W1" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="30" t="s">
+      <c r="X1" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="30" t="s">
+      <c r="Y1" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="30" t="s">
+      <c r="Z1" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="30" t="s">
+      <c r="AA1" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="30" t="s">
+      <c r="AB1" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="30" t="s">
+      <c r="AC1" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="30" t="s">
+      <c r="AD1" s="30" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" s="32" customFormat="1">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31"/>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-      <c r="Y3" s="31"/>
-      <c r="Z3" s="31"/>
-      <c r="AA3" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1 J1 M1 O1 P1 S1 Y1"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1 M1 P1 R1 S1 V1 AB1"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V1048576">
       <formula1>bz</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R1048576">
       <formula1>ywzl</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>qd</formula1>
     </dataValidation>
   </dataValidations>
@@ -1859,25 +1876,25 @@
           <x14:formula1>
             <xm:f>填写说明!$A$7:$A$46</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I1048576</xm:sqref>
+          <xm:sqref>L2:L1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>填写说明!$A$48:$A$49</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
+          <xm:sqref>M2:M1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>填写说明!$A$51:$A$87</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M1048576</xm:sqref>
+          <xm:sqref>P2:P1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>填写说明!$A$106:$A$141</xm:f>
           </x14:formula1>
-          <xm:sqref>P2:P1048576</xm:sqref>
+          <xm:sqref>S2:S1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1887,36 +1904,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A329"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:A331"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="73.375" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="73.3984375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75">
+    <row r="1" spans="1:1">
       <c r="A1" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="30">
+    <row r="2" spans="1:1" ht="31.8">
       <c r="A2" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.75">
+    <row r="3" spans="1:1">
       <c r="A3" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.75">
+    <row r="4" spans="1:1">
       <c r="A4" s="9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.75">
+    <row r="5" spans="1:1">
       <c r="A5" s="10"/>
     </row>
-    <row r="6" spans="1:1" ht="15.75">
+    <row r="6" spans="1:1">
       <c r="A6" s="11" t="s">
         <v>37</v>
       </c>
@@ -3527,7 +3544,17 @@
       </c>
     </row>
     <row r="329" spans="1:1">
-      <c r="A329" s="27" t="s">
+      <c r="A329" s="26" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" s="31" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" s="27" t="s">
         <v>317</v>
       </c>
     </row>
@@ -3541,9 +3568,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="14.625" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="14.59765625" customWidth="1" collapsed="1"/>
     <col min="2" max="2" width="34" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
